--- a/artfynd/A 30227-2026 artfynd.xlsx
+++ b/artfynd/A 30227-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105965638</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,8 +876,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105965640</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30227-2026 artfynd.xlsx
+++ b/artfynd/A 30227-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105965638</v>
+        <v>135864528</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>79473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Orsa, Ackamäck, Dlr</t>
+          <t>Ackomäck, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478247</v>
+        <v>478264</v>
       </c>
       <c r="R2" t="n">
-        <v>6819246</v>
+        <v>6819280</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,49 +775,49 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105965638</t>
+          <t>https://artportalen.se/Sighting/135864528</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105965640</v>
+        <v>105965638</v>
       </c>
       <c r="B3" t="n">
-        <v>80461</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478252</v>
+        <v>478247</v>
       </c>
       <c r="R3" t="n">
-        <v>6819240</v>
+        <v>6819246</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -878,7 +888,2417 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/105965638</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135864488</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>478593</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6819078</v>
+      </c>
+      <c r="S4" t="n">
+        <v>12</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864488</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135864510</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>478430</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6819083</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864510</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135864525</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>478261</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6819249</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864525</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135864526</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>478261</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6819251</v>
+      </c>
+      <c r="S7" t="n">
+        <v>12</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864526</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135864529</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>478264</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6819278</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864529</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135864507</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80450</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>478438</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6819097</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864507</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135864508</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80450</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>478430</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6819098</v>
+      </c>
+      <c r="S10" t="n">
+        <v>38</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864508</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135864527</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>478274</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6819289</v>
+      </c>
+      <c r="S11" t="n">
+        <v>14</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864527</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>105965640</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Orsa, Ackamäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>478252</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6819240</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/105965640</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135864484</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80568</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>478567</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6819087</v>
+      </c>
+      <c r="S13" t="n">
+        <v>28</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864484</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135864486</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80568</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>478565</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6819081</v>
+      </c>
+      <c r="S14" t="n">
+        <v>8</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864486</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135864491</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80568</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>478593</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6819091</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864491</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135864490</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>478602</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6819079</v>
+      </c>
+      <c r="S16" t="n">
+        <v>8</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Över 100 blomstjälkar</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864490</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135864493</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>478546</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6819116</v>
+      </c>
+      <c r="S17" t="n">
+        <v>23</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864493</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135864495</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>478546</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6819107</v>
+      </c>
+      <c r="S18" t="n">
+        <v>21</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864495</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135864496</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>478516</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6819120</v>
+      </c>
+      <c r="S19" t="n">
+        <v>14</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864496</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135864497</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>478509</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6819129</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864497</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135864498</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>478527</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6819127</v>
+      </c>
+      <c r="S21" t="n">
+        <v>17</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864498</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135864500</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>478505</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6819140</v>
+      </c>
+      <c r="S22" t="n">
+        <v>16</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864500</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135864509</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98142</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>478433</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6819118</v>
+      </c>
+      <c r="S23" t="n">
+        <v>9</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864509</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135864492</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99296</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>478560</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6819100</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864492</t>
         </is>
       </c>
     </row>
@@ -886,6 +3306,27 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30227-2026 artfynd.xlsx
+++ b/artfynd/A 30227-2026 artfynd.xlsx
@@ -2231,7 +2231,7 @@
         <v>135864490</v>
       </c>
       <c r="B16" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>135864493</v>
       </c>
       <c r="B17" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135864495</v>
       </c>
       <c r="B18" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>135864496</v>
       </c>
       <c r="B19" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>135864497</v>
       </c>
       <c r="B20" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>135864498</v>
       </c>
       <c r="B21" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>135864500</v>
       </c>
       <c r="B22" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>135864509</v>
       </c>
       <c r="B23" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>135864492</v>
       </c>
       <c r="B24" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 30227-2026 artfynd.xlsx
+++ b/artfynd/A 30227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135864528</v>
       </c>
       <c r="B2" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135864488</v>
       </c>
       <c r="B4" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135864510</v>
       </c>
       <c r="B5" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135864525</v>
       </c>
       <c r="B6" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135864526</v>
       </c>
       <c r="B7" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>135864529</v>
       </c>
       <c r="B8" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>135864507</v>
       </c>
       <c r="B9" t="n">
-        <v>80450</v>
+        <v>80452</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>135864508</v>
       </c>
       <c r="B10" t="n">
-        <v>80450</v>
+        <v>80452</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>135864527</v>
       </c>
       <c r="B11" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>135864484</v>
       </c>
       <c r="B13" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>135864486</v>
       </c>
       <c r="B14" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135864491</v>
       </c>
       <c r="B15" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135864490</v>
       </c>
       <c r="B16" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>135864493</v>
       </c>
       <c r="B17" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135864495</v>
       </c>
       <c r="B18" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>135864496</v>
       </c>
       <c r="B19" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>135864497</v>
       </c>
       <c r="B20" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>135864498</v>
       </c>
       <c r="B21" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>135864500</v>
       </c>
       <c r="B22" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>135864509</v>
       </c>
       <c r="B23" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>135864492</v>
       </c>
       <c r="B24" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 30227-2026 artfynd.xlsx
+++ b/artfynd/A 30227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135864528</v>
       </c>
       <c r="B2" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135864488</v>
       </c>
       <c r="B4" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135864510</v>
       </c>
       <c r="B5" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135864525</v>
       </c>
       <c r="B6" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135864526</v>
       </c>
       <c r="B7" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>135864529</v>
       </c>
       <c r="B8" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>135864507</v>
       </c>
       <c r="B9" t="n">
-        <v>80452</v>
+        <v>80453</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>135864508</v>
       </c>
       <c r="B10" t="n">
-        <v>80452</v>
+        <v>80453</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>135864527</v>
       </c>
       <c r="B11" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>135864484</v>
       </c>
       <c r="B13" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>135864486</v>
       </c>
       <c r="B14" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135864491</v>
       </c>
       <c r="B15" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135864490</v>
       </c>
       <c r="B16" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>135864493</v>
       </c>
       <c r="B17" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135864495</v>
       </c>
       <c r="B18" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>135864496</v>
       </c>
       <c r="B19" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>135864497</v>
       </c>
       <c r="B20" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>135864498</v>
       </c>
       <c r="B21" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>135864500</v>
       </c>
       <c r="B22" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>135864509</v>
       </c>
       <c r="B23" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>135864492</v>
       </c>
       <c r="B24" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 30227-2026 artfynd.xlsx
+++ b/artfynd/A 30227-2026 artfynd.xlsx
@@ -2231,7 +2231,7 @@
         <v>135864490</v>
       </c>
       <c r="B16" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>135864493</v>
       </c>
       <c r="B17" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135864495</v>
       </c>
       <c r="B18" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>135864496</v>
       </c>
       <c r="B19" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>135864497</v>
       </c>
       <c r="B20" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>135864498</v>
       </c>
       <c r="B21" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>135864500</v>
       </c>
       <c r="B22" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>135864509</v>
       </c>
       <c r="B23" t="n">
-        <v>98162</v>
+        <v>98163</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>135864492</v>
       </c>
       <c r="B24" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 30227-2026 artfynd.xlsx
+++ b/artfynd/A 30227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135864528</v>
       </c>
       <c r="B2" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135864488</v>
       </c>
       <c r="B4" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135864510</v>
       </c>
       <c r="B5" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135864525</v>
       </c>
       <c r="B6" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135864526</v>
       </c>
       <c r="B7" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>135864529</v>
       </c>
       <c r="B8" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>135864507</v>
       </c>
       <c r="B9" t="n">
-        <v>80453</v>
+        <v>80454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>135864508</v>
       </c>
       <c r="B10" t="n">
-        <v>80453</v>
+        <v>80454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>135864527</v>
       </c>
       <c r="B11" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>135864484</v>
       </c>
       <c r="B13" t="n">
-        <v>80571</v>
+        <v>80572</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>135864486</v>
       </c>
       <c r="B14" t="n">
-        <v>80571</v>
+        <v>80572</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135864491</v>
       </c>
       <c r="B15" t="n">
-        <v>80571</v>
+        <v>80572</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135864490</v>
       </c>
       <c r="B16" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>135864493</v>
       </c>
       <c r="B17" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135864495</v>
       </c>
       <c r="B18" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>135864496</v>
       </c>
       <c r="B19" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>135864497</v>
       </c>
       <c r="B20" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>135864498</v>
       </c>
       <c r="B21" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>135864500</v>
       </c>
       <c r="B22" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>135864509</v>
       </c>
       <c r="B23" t="n">
-        <v>98163</v>
+        <v>98164</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>135864492</v>
       </c>
       <c r="B24" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 30227-2026 artfynd.xlsx
+++ b/artfynd/A 30227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135864528</v>
       </c>
       <c r="B2" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135864488</v>
       </c>
       <c r="B4" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135864510</v>
       </c>
       <c r="B5" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135864525</v>
       </c>
       <c r="B6" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135864526</v>
       </c>
       <c r="B7" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>135864529</v>
       </c>
       <c r="B8" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>135864507</v>
       </c>
       <c r="B9" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>135864508</v>
       </c>
       <c r="B10" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>135864527</v>
       </c>
       <c r="B11" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>135864484</v>
       </c>
       <c r="B13" t="n">
-        <v>80572</v>
+        <v>80576</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>135864486</v>
       </c>
       <c r="B14" t="n">
-        <v>80572</v>
+        <v>80576</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135864491</v>
       </c>
       <c r="B15" t="n">
-        <v>80572</v>
+        <v>80576</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135864490</v>
       </c>
       <c r="B16" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>135864493</v>
       </c>
       <c r="B17" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135864495</v>
       </c>
       <c r="B18" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>135864496</v>
       </c>
       <c r="B19" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>135864497</v>
       </c>
       <c r="B20" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>135864498</v>
       </c>
       <c r="B21" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>135864500</v>
       </c>
       <c r="B22" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>135864509</v>
       </c>
       <c r="B23" t="n">
-        <v>98164</v>
+        <v>98170</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>135864492</v>
       </c>
       <c r="B24" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 30227-2026 artfynd.xlsx
+++ b/artfynd/A 30227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135864528</v>
       </c>
       <c r="B2" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135864488</v>
       </c>
       <c r="B4" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135864510</v>
       </c>
       <c r="B5" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135864525</v>
       </c>
       <c r="B6" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135864526</v>
       </c>
       <c r="B7" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>135864529</v>
       </c>
       <c r="B8" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>135864507</v>
       </c>
       <c r="B9" t="n">
-        <v>80458</v>
+        <v>80459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>135864508</v>
       </c>
       <c r="B10" t="n">
-        <v>80458</v>
+        <v>80459</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>135864527</v>
       </c>
       <c r="B11" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>135864484</v>
       </c>
       <c r="B13" t="n">
-        <v>80576</v>
+        <v>80577</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>135864486</v>
       </c>
       <c r="B14" t="n">
-        <v>80576</v>
+        <v>80577</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135864491</v>
       </c>
       <c r="B15" t="n">
-        <v>80576</v>
+        <v>80577</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135864490</v>
       </c>
       <c r="B16" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>135864493</v>
       </c>
       <c r="B17" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135864495</v>
       </c>
       <c r="B18" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>135864496</v>
       </c>
       <c r="B19" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>135864497</v>
       </c>
       <c r="B20" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>135864498</v>
       </c>
       <c r="B21" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>135864500</v>
       </c>
       <c r="B22" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>135864509</v>
       </c>
       <c r="B23" t="n">
-        <v>98170</v>
+        <v>98171</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>135864492</v>
       </c>
       <c r="B24" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 30227-2026 artfynd.xlsx
+++ b/artfynd/A 30227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135864528</v>
       </c>
       <c r="B2" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135864488</v>
       </c>
       <c r="B4" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135864510</v>
       </c>
       <c r="B5" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135864525</v>
       </c>
       <c r="B6" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135864526</v>
       </c>
       <c r="B7" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>135864529</v>
       </c>
       <c r="B8" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>135864507</v>
       </c>
       <c r="B9" t="n">
-        <v>80459</v>
+        <v>80463</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>135864508</v>
       </c>
       <c r="B10" t="n">
-        <v>80459</v>
+        <v>80463</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>135864527</v>
       </c>
       <c r="B11" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>135864484</v>
       </c>
       <c r="B13" t="n">
-        <v>80577</v>
+        <v>80581</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>135864486</v>
       </c>
       <c r="B14" t="n">
-        <v>80577</v>
+        <v>80581</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135864491</v>
       </c>
       <c r="B15" t="n">
-        <v>80577</v>
+        <v>80581</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135864490</v>
       </c>
       <c r="B16" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>135864493</v>
       </c>
       <c r="B17" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135864495</v>
       </c>
       <c r="B18" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>135864496</v>
       </c>
       <c r="B19" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>135864497</v>
       </c>
       <c r="B20" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>135864498</v>
       </c>
       <c r="B21" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>135864500</v>
       </c>
       <c r="B22" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>135864509</v>
       </c>
       <c r="B23" t="n">
-        <v>98171</v>
+        <v>98182</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>135864492</v>
       </c>
       <c r="B24" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 30227-2026 artfynd.xlsx
+++ b/artfynd/A 30227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135864528</v>
       </c>
       <c r="B2" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135864488</v>
       </c>
       <c r="B4" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135864510</v>
       </c>
       <c r="B5" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135864525</v>
       </c>
       <c r="B6" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135864526</v>
       </c>
       <c r="B7" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>135864529</v>
       </c>
       <c r="B8" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>135864507</v>
       </c>
       <c r="B9" t="n">
-        <v>80463</v>
+        <v>80469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>135864508</v>
       </c>
       <c r="B10" t="n">
-        <v>80463</v>
+        <v>80469</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>135864527</v>
       </c>
       <c r="B11" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>135864484</v>
       </c>
       <c r="B13" t="n">
-        <v>80581</v>
+        <v>80587</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>135864486</v>
       </c>
       <c r="B14" t="n">
-        <v>80581</v>
+        <v>80587</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135864491</v>
       </c>
       <c r="B15" t="n">
-        <v>80581</v>
+        <v>80587</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135864490</v>
       </c>
       <c r="B16" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>135864493</v>
       </c>
       <c r="B17" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135864495</v>
       </c>
       <c r="B18" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>135864496</v>
       </c>
       <c r="B19" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>135864497</v>
       </c>
       <c r="B20" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>135864498</v>
       </c>
       <c r="B21" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>135864500</v>
       </c>
       <c r="B22" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>135864509</v>
       </c>
       <c r="B23" t="n">
-        <v>98182</v>
+        <v>98195</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>135864492</v>
       </c>
       <c r="B24" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 30227-2026 artfynd.xlsx
+++ b/artfynd/A 30227-2026 artfynd.xlsx
@@ -2231,7 +2231,7 @@
         <v>135864490</v>
       </c>
       <c r="B16" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>135864493</v>
       </c>
       <c r="B17" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135864495</v>
       </c>
       <c r="B18" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>135864496</v>
       </c>
       <c r="B19" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>135864497</v>
       </c>
       <c r="B20" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>135864498</v>
       </c>
       <c r="B21" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>135864500</v>
       </c>
       <c r="B22" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>135864509</v>
       </c>
       <c r="B23" t="n">
-        <v>98195</v>
+        <v>98196</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>135864492</v>
       </c>
       <c r="B24" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 30227-2026 artfynd.xlsx
+++ b/artfynd/A 30227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135864528</v>
       </c>
       <c r="B2" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135864488</v>
       </c>
       <c r="B4" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135864510</v>
       </c>
       <c r="B5" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135864525</v>
       </c>
       <c r="B6" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135864526</v>
       </c>
       <c r="B7" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>135864529</v>
       </c>
       <c r="B8" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>135864507</v>
       </c>
       <c r="B9" t="n">
-        <v>80469</v>
+        <v>80482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>135864508</v>
       </c>
       <c r="B10" t="n">
-        <v>80469</v>
+        <v>80482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>135864527</v>
       </c>
       <c r="B11" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>135864484</v>
       </c>
       <c r="B13" t="n">
-        <v>80587</v>
+        <v>80600</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>135864486</v>
       </c>
       <c r="B14" t="n">
-        <v>80587</v>
+        <v>80600</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135864491</v>
       </c>
       <c r="B15" t="n">
-        <v>80587</v>
+        <v>80600</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135864490</v>
       </c>
       <c r="B16" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>135864493</v>
       </c>
       <c r="B17" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135864495</v>
       </c>
       <c r="B18" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>135864496</v>
       </c>
       <c r="B19" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>135864497</v>
       </c>
       <c r="B20" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>135864498</v>
       </c>
       <c r="B21" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>135864500</v>
       </c>
       <c r="B22" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>135864509</v>
       </c>
       <c r="B23" t="n">
-        <v>98196</v>
+        <v>98209</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>135864492</v>
       </c>
       <c r="B24" t="n">
-        <v>99350</v>
+        <v>99363</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 30227-2026 artfynd.xlsx
+++ b/artfynd/A 30227-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135864528</v>
       </c>
       <c r="B2" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135864488</v>
       </c>
       <c r="B4" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135864510</v>
       </c>
       <c r="B5" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135864525</v>
       </c>
       <c r="B6" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135864526</v>
       </c>
       <c r="B7" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>135864529</v>
       </c>
       <c r="B8" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>135864507</v>
       </c>
       <c r="B9" t="n">
-        <v>80482</v>
+        <v>80483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>135864508</v>
       </c>
       <c r="B10" t="n">
-        <v>80482</v>
+        <v>80483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>135864527</v>
       </c>
       <c r="B11" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>135864484</v>
       </c>
       <c r="B13" t="n">
-        <v>80600</v>
+        <v>80601</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>135864486</v>
       </c>
       <c r="B14" t="n">
-        <v>80600</v>
+        <v>80601</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135864491</v>
       </c>
       <c r="B15" t="n">
-        <v>80600</v>
+        <v>80601</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135864490</v>
       </c>
       <c r="B16" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>135864493</v>
       </c>
       <c r="B17" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135864495</v>
       </c>
       <c r="B18" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>135864496</v>
       </c>
       <c r="B19" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>135864497</v>
       </c>
       <c r="B20" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>135864498</v>
       </c>
       <c r="B21" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>135864500</v>
       </c>
       <c r="B22" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>135864509</v>
       </c>
       <c r="B23" t="n">
-        <v>98209</v>
+        <v>98210</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>135864492</v>
       </c>
       <c r="B24" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
